--- a/output/pdf_financials_xlsx/RFLX.xlsx
+++ b/output/pdf_financials_xlsx/RFLX.xlsx
@@ -2072,13 +2072,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.884722</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.948829</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.948829</v>
       </c>
     </row>
     <row r="93">
@@ -3208,7 +3208,11 @@
           <t>Reserves 10</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -4312,7 +4316,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E53" s="5" t="n">
         <v>0.884722</v>
       </c>

--- a/output/pdf_financials_xlsx/RFLX.xlsx
+++ b/output/pdf_financials_xlsx/RFLX.xlsx
@@ -1120,13 +1120,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.06510000000000001</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.002387</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.015228</v>
       </c>
     </row>
     <row r="35">
@@ -1152,13 +1152,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.06510000000000001</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.002387</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.015228</v>
       </c>
     </row>
     <row r="37">
@@ -1344,13 +1344,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.080288</v>
+        <v>0.015188</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.019424</v>
+        <v>0.017037</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.015228</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -2976,7 +2976,11 @@
           <t>Reclamation deposits 7</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>-</t>
@@ -4138,7 +4142,11 @@
           <t>Reclamation deposits 6</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E47" s="5" t="n">
         <v>0.265309</v>
       </c>
@@ -5205,7 +5213,11 @@
           <t>Foreign exchange (gain)/loss on reclamation deposits</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
           <t>-</t>
@@ -5420,7 +5432,11 @@
           <t>Reclamation deposits 7</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
           <t>-</t>
@@ -5846,7 +5862,11 @@
           <t>Foreign exchange gain on reclamation deposits</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
           <t>-</t>
@@ -5937,7 +5957,11 @@
           <t>Reclamation deposits 6</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E106" s="5" t="n">
         <v>-0.265309</v>
       </c>
